--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
@@ -10240,7 +10240,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
@@ -10240,7 +10240,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10240,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10240,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10240,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10240,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10240,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250930_171243.xlsx
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
